--- a/Database/Order_traction.xlsx
+++ b/Database/Order_traction.xlsx
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20-04-2026 09:23:01</t>
+          <t>21-04-2026 13:26:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SCI.NS</t>
+          <t>PNBHOUSING.NS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>988</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/Database/Order_traction.xlsx
+++ b/Database/Order_traction.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,27 +446,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-04-2026 13:26:08</t>
+          <t>20-04-2026 09:23:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNBHOUSING.NS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>988</t>
-        </is>
+          <t>SCI.NS</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>21-04-2026 09:20:08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JSWCEMENT.NS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>136</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>21-04-2026 09:23:13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JSWCEMENT.NS</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>130</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>21-04-2026 09:23:43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SCI.NS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>297</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>21-04-2026 09:44:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DATAPATTNS.NS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
